--- a/resources/templates/standard/J1100-10.xlsx
+++ b/resources/templates/standard/J1100-10.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제품 법/규제 요구사항 목록표</t>
   </si>
@@ -559,12 +562,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -584,21 +589,21 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="3"/>
       <c r="Y1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -675,7 +680,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -688,7 +693,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -701,7 +706,7 @@
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
       <c r="W4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
@@ -716,7 +721,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -729,7 +734,7 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
@@ -742,7 +747,7 @@
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
@@ -757,15 +762,15 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -773,7 +778,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -781,26 +786,26 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
